--- a/data/trans_orig/IP05A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>34506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>42207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>62133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43929</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29378</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>44787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63319</t>
+          <t>63374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19939</t>
+          <t>19971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>33594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32221</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41760</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60907</t>
+          <t>61498</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118374</t>
+          <t>118206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150326</t>
+          <t>148150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>127577</t>
+          <t>127986</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159390</t>
+          <t>158128</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>255362</t>
+          <t>254181</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299185</t>
+          <t>299522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>186630</t>
+          <t>189231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>218636</t>
+          <t>220719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227958</t>
+          <t>228036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>261659</t>
+          <t>263046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>425877</t>
+          <t>425265</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>474361</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64639</t>
+          <t>65673</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90178</t>
+          <t>91113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73406</t>
+          <t>75156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>100803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146733</t>
+          <t>147324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184832</t>
+          <t>183766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>51261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41553</t>
+          <t>41563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60476</t>
+          <t>59392</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77934</t>
+          <t>80323</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>106406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>32,07%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93332</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114929</t>
+          <t>114486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68951</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89205</t>
+          <t>89766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169688</t>
+          <t>169257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198252</t>
+          <t>198119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35315</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36480</t>
+          <t>35759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45602</t>
+          <t>44774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>181875</t>
+          <t>184998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200312</t>
+          <t>199534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242443</t>
+          <t>237732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>395775</t>
+          <t>394038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>448300</t>
+          <t>449451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325203</t>
+          <t>323204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367357</t>
+          <t>365301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>337159</t>
+          <t>340538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381765</t>
+          <t>380775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>676114</t>
+          <t>675436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>731184</t>
+          <t>736547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>115426</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>124501</t>
+          <t>124673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157830</t>
+          <t>158062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>249529</t>
+          <t>249000</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>295528</t>
+          <t>294928</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36701</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21909</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35445</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67953</t>
+          <t>67422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37449</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53870</t>
+          <t>52075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34136</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50027</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>75779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98221</t>
+          <t>98012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>43014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140387</t>
+          <t>140035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173768</t>
+          <t>172182</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135719</t>
+          <t>134657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>169850</t>
+          <t>168976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284059</t>
+          <t>284153</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>331457</t>
+          <t>330083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167216</t>
+          <t>165745</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201298</t>
+          <t>198763</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210258</t>
+          <t>209669</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246427</t>
+          <t>246581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>386640</t>
+          <t>386499</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>436656</t>
+          <t>437133</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96644</t>
+          <t>98477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127225</t>
+          <t>128697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100055</t>
+          <t>100013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129763</t>
+          <t>131097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205722</t>
+          <t>206080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250664</t>
+          <t>249310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42335</t>
+          <t>41700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62005</t>
+          <t>62509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38476</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86761</t>
+          <t>86794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113961</t>
+          <t>114883</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62187</t>
+          <t>62151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83820</t>
+          <t>82980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68735</t>
+          <t>67557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89553</t>
+          <t>89403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>136662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165702</t>
+          <t>165456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>33290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52761</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>35171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54858</t>
+          <t>54360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74319</t>
+          <t>74816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>100298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>216955</t>
+          <t>216147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257434</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209158</t>
+          <t>209038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>249778</t>
+          <t>249436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>437135</t>
+          <t>438526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495805</t>
+          <t>495304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>277893</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>321051</t>
+          <t>323387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325925</t>
+          <t>324660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>371007</t>
+          <t>371303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>618894</t>
+          <t>617672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>677203</t>
+          <t>679949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>193515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155094</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>194780</t>
+          <t>196179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323797</t>
+          <t>320484</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>380619</t>
+          <t>376188</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>38929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65086</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13870</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52792</t>
+          <t>52517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16541</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>22676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170064</t>
+          <t>169440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204207</t>
+          <t>203864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168451</t>
+          <t>168957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>203986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349243</t>
+          <t>349402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398580</t>
+          <t>398703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169576</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205460</t>
+          <t>204003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177206</t>
+          <t>177837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212651</t>
+          <t>214992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>356157</t>
+          <t>358179</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>407170</t>
+          <t>406718</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83903</t>
+          <t>83036</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111858</t>
+          <t>110335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92880</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122415</t>
+          <t>121612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182127</t>
+          <t>183349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224124</t>
+          <t>222428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48488</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69528</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46161</t>
+          <t>46058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67400</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101092</t>
+          <t>101006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>129822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82030</t>
+          <t>82174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65372</t>
+          <t>67067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88679</t>
+          <t>88957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132544</t>
+          <t>134336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163545</t>
+          <t>165467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52327</t>
+          <t>51952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64454</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82420</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>108928</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>249014</t>
+          <t>248773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290055</t>
+          <t>292226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253670</t>
+          <t>252629</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297778</t>
+          <t>296964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>516380</t>
+          <t>515515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>575268</t>
+          <t>575406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>262204</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>302847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>270102</t>
+          <t>270678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313867</t>
+          <t>314509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>546295</t>
+          <t>543964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604179</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168328</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158460</t>
+          <t>158795</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>196631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>301096</t>
+          <t>301763</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>352918</t>
+          <t>351347</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37151</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50393</t>
+          <t>50731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66434</t>
+          <t>66609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>90584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36827</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>16714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266481</t>
+          <t>275742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372209</t>
+          <t>372602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405609</t>
+          <t>405962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439792</t>
+          <t>438096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691654</t>
+          <t>700760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798935</t>
+          <t>799677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>54573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>165499</t>
+          <t>158185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51452</t>
+          <t>52699</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80463</t>
+          <t>80063</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>116163</t>
+          <t>115715</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>224485</t>
+          <t>223520</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>20266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48704</t>
+          <t>50482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76437</t>
+          <t>77912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105853</t>
+          <t>105958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122798</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120289</t>
+          <t>120880</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143593</t>
+          <t>144739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>232677</t>
+          <t>232521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>263537</t>
+          <t>261887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29975</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20339</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>20105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>29882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>431590</t>
+          <t>433761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>525962</t>
+          <t>527522</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>580265</t>
+          <t>579026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>622231</t>
+          <t>622807</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1031056</t>
+          <t>1032372</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1135895</t>
+          <t>1132857</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>194931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181009</t>
+          <t>181538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301988</t>
+          <t>282317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>130997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25684</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19666</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33073</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26754</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20348</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34506</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33613</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38,2%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25684</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19049</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>32717</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42207</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>62306</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36478</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28637</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>43487</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36719</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>29626</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>44926</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29859</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>44236</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36478</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29546</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44787</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>42,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63374</t>
+          <t>62898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84492</t>
+          <t>83343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18516</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19971</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>33594</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20075</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>34139</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>29,74%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24683</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17768</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>32490</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42278</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61498</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>142762</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127093</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>161185</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,06%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>134070</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>118206</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>148150</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>120228</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>150683</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,27%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>142762</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>127986</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>158128</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>254181</t>
+          <t>255189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299522</t>
+          <t>298972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>244514</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>225140</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>262827</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>51,48%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>203985</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189231</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>220719</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>187351</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>218889</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>49,1%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>45,55%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>53,13%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>244514</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>228036</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>263046</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>51,48%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>424487</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>471518</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87690</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74528</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>101926</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>77379</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65673</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91113</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>65387</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90941</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,63%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87690</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75156</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>100803</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147324</t>
+          <t>146158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183766</t>
+          <t>183097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>474966</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>474966</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>474966</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>415434</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>415434</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>415434</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>474966</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>474966</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>474966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50444</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41213</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>60262</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>26,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>41818</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>33060</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51261</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>34002</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>51459</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>24,09%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,53%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50444</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>41563</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>59392</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>80323</t>
+          <t>80379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106406</t>
+          <t>106342</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>79718</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>69749</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>90311</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>104400</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93437</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>114486</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>93479</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>114428</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>53,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>79718</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>70260</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>89766</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169257</t>
+          <t>169565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198119</t>
+          <t>197946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27976</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20653</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36339</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>27401</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20373</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35703</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19957</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35598</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>15,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27976</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21546</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35759</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44774</t>
+          <t>44848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66783</t>
+          <t>67085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173619</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>218890</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>198970</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>239387</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,25%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>299</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>202641</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>184998</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>223248</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>184915</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>222560</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>29,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>218890</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>199534</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>237732</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394038</t>
+          <t>395874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>449451</t>
+          <t>448158</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>360710</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>340002</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>383400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>518</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>345105</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>323204</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>365301</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322712</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>363976</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,8%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>47,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>360710</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>340538</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>380775</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>675436</t>
+          <t>678204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736547</t>
+          <t>735821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>140349</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123867</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>156940</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>131647</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>113549</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>148841</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>114770</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>149360</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,38%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>140349</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>124673</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158062</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>249000</t>
+          <t>247447</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>294928</t>
+          <t>294933</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>719949</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>719949</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>719949</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>679393</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>679393</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>679393</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>719949</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>719949</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>719949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28241</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21527</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36370</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>28686</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21916</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36267</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22066</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36243</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28241</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67422</t>
+          <t>66646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41714</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34175</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49924</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45020</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37187</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52075</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37379</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53056</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41714</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33572</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>49282</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>48,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75966</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98012</t>
+          <t>97628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23392</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,84%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,14%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17895</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12311</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24998</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12039</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24932</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>19,54%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>27,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11111</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23274</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43014</t>
+          <t>43057</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>151839</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>135923</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168787</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,49%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>156146</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>140035</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172182</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>140957</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>172848</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>151839</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>134657</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>168976</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284153</t>
+          <t>283838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330083</t>
+          <t>330745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,97%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>227756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>209506</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>247174</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>46,06%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>42,37%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>49,99%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>182902</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>165745</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>198763</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>165982</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>201989</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>40,52%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>227756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>209669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>246581</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>386499</t>
+          <t>384614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>437133</t>
+          <t>436559</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,15%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114851</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>98925</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>130661</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>112372</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98477</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128697</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96815</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>128333</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>24,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>114851</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>100013</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>131097</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206080</t>
+          <t>205498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249310</t>
+          <t>250169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>451420</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>451420</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>451420</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>48893</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40158</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59263</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>51647</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41700</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>62509</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>41891</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>61686</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,96%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>48893</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39677</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>58871</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86794</t>
+          <t>88116</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114883</t>
+          <t>116684</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>78957</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67246</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88903</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72491</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62151</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82980</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62155</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>83423</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>43,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>37,26%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>78957</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>67557</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>89403</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,84%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136662</t>
+          <t>135577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165456</t>
+          <t>166440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>44378</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54983</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>42673</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33290</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52038</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33257</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>52340</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>44378</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35171</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>54360</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74816</t>
+          <t>74236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100298</t>
+          <t>101767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>228972</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>208999</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>248920</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>349</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>236479</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>216147</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>257005</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>216351</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>257158</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>33,31%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>228972</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>209038</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>249436</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438526</t>
+          <t>438118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495304</t>
+          <t>495068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>348427</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>326045</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>370323</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46,28%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>49,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>429</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>300414</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>280953</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>323387</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>279122</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>323245</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>42,32%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>348427</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>324660</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>371303</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>46,28%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>617672</t>
+          <t>619407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>679949</t>
+          <t>678336</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,38%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>175467</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>155665</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>194627</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,85%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>172940</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>154053</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>193515</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>156080</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>193048</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>24,36%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>175467</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>156872</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>196179</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>320484</t>
+          <t>320707</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>376188</t>
+          <t>373180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>709833</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>709833</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>709833</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32015</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25010</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39113</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24907</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19125</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31376</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18617</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30959</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24843</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38929</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47990</t>
+          <t>47881</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67495</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20035</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14247</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26965</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23277</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17582</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29080</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29352</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13737</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26600</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34445</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52517</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16565</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10683</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22985</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,14%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,57%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11194</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6821</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17394</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16687</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16565</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11119</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22676</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>21143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>187286</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>170107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>205338</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>186338</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>169440</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>203864</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>169533</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202913</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>39,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>43,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>187286</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>168957</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203986</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349402</t>
+          <t>349574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398703</t>
+          <t>398935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>194143</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178501</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>213295</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>170259</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>204003</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>170428</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>206636</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>39,85%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>194143</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177837</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>214992</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>358179</t>
+          <t>354584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>406718</t>
+          <t>405507</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>106628</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>92529</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>121276</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>96281</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83036</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>110335</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>82286</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>111044</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>106628</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>92165</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>121612</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>184126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>222428</t>
+          <t>224122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>469855</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>469855</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>469855</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55927</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45555</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>65815</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29,83%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>59005</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>49617</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70004</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>48432</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>69446</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>34,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>55927</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>46058</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>65917</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>29,83%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>100911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129822</t>
+          <t>130421</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>77812</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>67147</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>89587</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>71481</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>61223</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82174</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>61984</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>82653</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>41,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>77812</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>67067</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>88957</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134336</t>
+          <t>133973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165467</t>
+          <t>165147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>53755</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44331</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64928</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>42217</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34245</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51952</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32904</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>50506</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>24,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>53755</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>43772</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>64198</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83499</t>
+          <t>82029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109684</t>
+          <t>109311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>275228</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>295965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>270250</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>248773</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>292226</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>250902</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>290566</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>275228</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>252629</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>296964</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,98%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>515515</t>
+          <t>516151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>575406</t>
+          <t>576628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>291990</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>270248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>313330</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>416</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>281994</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>261132</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>302847</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>260057</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>303409</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>37,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>291990</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>270678</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>314509</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>543964</t>
+          <t>543563</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>603837</t>
+          <t>603469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>176948</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158203</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>197867</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149692</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>133665</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>167702</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>134273</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>167500</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>21,33%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>176948</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158795</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>196631</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>301763</t>
+          <t>299129</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>351347</t>
+          <t>352795</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>701936</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>701936</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>701936</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40940</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34778</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46251</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>61,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36182</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24618</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44425</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>81,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44283</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>29731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50731</t>
+          <t>39779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>80465</t>
+          <t>76228</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>68260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90584</t>
+          <t>83242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10181</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>14491</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6292</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27786</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37438</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9586</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15675</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4005</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9026</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,51%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56205</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61479</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>102963</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>102963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116157</t>
+          <t>102963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>387874</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>371062</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>401259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>84,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>519</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>345382</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>275742</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>372602</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>423072</t>
+          <t>342492</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405962</t>
+          <t>325815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>438096</t>
+          <t>356597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>768454</t>
+          <t>730366</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700760</t>
+          <t>707557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799677</t>
+          <t>751914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>62244</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50455</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>76066</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>81496</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>54573</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158185</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>34,35%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65179</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80063</t>
+          <t>73386</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>146675</t>
+          <t>120848</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>115715</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223520</t>
+          <t>141062</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18430</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35155</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33632</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24157</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>45868</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>31352</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>41295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62000</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50482</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77912</t>
+          <t>70382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>113389</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132843</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>73,79%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67,71%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>79,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>115482</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>105958</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>123861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>77,22%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>70,85%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>82,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132910</t>
+          <t>116085</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120880</t>
+          <t>107992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>144739</t>
+          <t>124745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>248393</t>
+          <t>239657</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>232521</t>
+          <t>226953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261887</t>
+          <t>252972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23940</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16824</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33841</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20637</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13955</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28857</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28309</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>28743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48946</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>34542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63512</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19950</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13261</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28286</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13432</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8239</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20105</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29882</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34618</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25618</t>
+          <t>25160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>43943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>552385</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>530633</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>570850</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>78,99%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>75,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>497046</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>433761</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>527522</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>74,77%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>600265</t>
+          <t>493865</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>579026</t>
+          <t>475714</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>622807</t>
+          <t>512100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1097312</t>
+          <t>1046250</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1032372</t>
+          <t>1021753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1132857</t>
+          <t>1071658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91864</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>76903</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>109117</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>116623</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>86040</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>194931</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>100369</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82847</t>
+          <t>71924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119506</t>
+          <t>102698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>216992</t>
+          <t>177745</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181538</t>
+          <t>157733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282317</t>
+          <t>201063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -8482,107 +8482,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>55096</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43107</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>68943</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51069</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>39649</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>64793</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48013</t>
+          <t>39031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75794</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>104531</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>88716</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>120745</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>110938</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>94428</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>130997</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>699345</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>699345</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>699345</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>760503</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>760503</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>760503</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425242</t>
+          <t>1328526</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425242</t>
+          <t>1328526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425242</t>
+          <t>1328526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
